--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-procedure.xlsx
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -310,16 +310,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -445,7 +445,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -473,7 +473,7 @@
 </t>
   </si>
   <si>
-    <t>この手順の外部識別子 / External Identifiers for this procedure</t>
+    <t>このプロシジャー（処置等）の外部identifier / External Identifiers for this procedure</t>
   </si>
   <si>
     <t>これは、ビジネスプロセスによって定義され、リソース自体への直接のURL参照が適切でない場合に参照するために使用される、このProcedureに関連する識別子を記録する。</t>
@@ -482,7 +482,7 @@
     <t>これはビジネス識別子であり、リソース識別子ではない（議論参照）。識別子は1つのリソースインスタンスにのみ表示されることがベストだが、ビジネス上の慣習により、同じ識別子を持つ複数のリソースインスタンスが存在することがあるかもしれない。例えば、複数のPatientとPersonリソースインスタンスが同じ社会保険番号を共有しているかもしれない。</t>
   </si>
   <si>
-    <t>さまざまな参加システムで知られており、サーバー全体で一貫性のある方法で知られている手順を識別できます。 / Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
+    <t>さまざまな参加システムで知られており、サーバー全体で一貫性のある方法で知られているプロシジャー（処置等）を識別できます。 / Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -525,7 +525,7 @@
     <t>本Procedure全体または一部を遵守する、外部で管理されているプロトコル、ガイドライン、オーダセット、またはその他の定義を指すURL。</t>
   </si>
   <si>
-    <t>これは、HTMLページ、PDFなどである可能性があるか、単に解決できないURI識別子である可能性があります。 / This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+    <t>これは、HTMLページ、PDFなどである可能性があるか、単に解決できないURIidentifierである可能性があります。 / This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
   </si>
   <si>
     <t>Event.instantiatesUri</t>
@@ -602,7 +602,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>手順の状態を指定するコード。 / A code specifying the state of the procedure.</t>
+    <t>プロシジャー（処置等）の状態を指定するコード。 / A code specifying the state of the procedure.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/event-status|4.0.1</t>
@@ -655,7 +655,7 @@
     <t>このプロシジャーの分類カテゴリ</t>
   </si>
   <si>
-    <t>検索、並べ替え、表示の手順を分類するコード（「外科的処置」など）。 / A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+    <t>検索、並べ替え、表示のプロシジャー（処置等）を分類するコード（「外科的処置」など）。 / A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCategory_VS</t>
@@ -1358,7 +1358,7 @@
 例:自宅での出生、レストランで気管切開など。</t>
   </si>
   <si>
-    <t>記録が保持される可能性が高い場所に手順を結びます。 / Ties a procedure to where the records are likely kept.</t>
+    <t>記録が保持される可能性が高い場所にプロシジャー（処置等）を結びます。 / Ties a procedure to where the records are likely kept.</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role[classCode=SDLOC]</t>
@@ -1518,7 +1518,7 @@
     <t>今後の処置が特別なフォローアップを必要とする場合（例：抜糸）、フォローアップはシンプルなnote として表現してもよいが、より複雑になる可能性もあり、その場合はケアプランリソースを使用することができる。</t>
   </si>
   <si>
-    <t>手順で特定のフォローアップが必要な場合 - 例えば縫合の除去。フォローアップは、単純なメモとして表されるか、潜在的により複雑になる可能性があります。その場合、カレプランリソースを使用できます。 / If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
+    <t>プロシジャー（処置等）で特定のフォローアップが必要な場合 - 例えば縫合の除去。フォローアップは、単純なメモとして表されるか、潜在的により複雑になる可能性があります。その場合、カレプランリソースを使用できます。 / If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS</t>
@@ -1971,7 +1971,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="59.70703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="69.609375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="66.18359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
